--- a/salidas/empresas/MMM.xlsx
+++ b/salidas/empresas/MMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.32833862304688</v>
+        <v>33.32834625244141</v>
       </c>
       <c r="C2" t="n">
         <v>60.8277587890625</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>33.92636108398438</v>
+        <v>33.92636489868164</v>
       </c>
       <c r="C3" t="n">
         <v>61.53010177612305</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>34.89448928833008</v>
+        <v>34.89449691772461</v>
       </c>
       <c r="C4" t="n">
         <v>63.28595352172852</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.38483428955078</v>
+        <v>39.38480758666992</v>
       </c>
       <c r="C5" t="n">
         <v>71.42976379394531</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.77440643310547</v>
+        <v>38.77438735961914</v>
       </c>
       <c r="C6" t="n">
         <v>69.94983673095703</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.4349479675293</v>
+        <v>37.43495178222656</v>
       </c>
       <c r="C7" t="n">
         <v>67.533447265625</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>32.62868881225586</v>
+        <v>32.62869644165039</v>
       </c>
       <c r="C8" t="n">
         <v>58.86287689208984</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>33.44704055786133</v>
+        <v>33.44704437255859</v>
       </c>
       <c r="C9" t="n">
         <v>59.94983291625977</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>34.71588134765625</v>
+        <v>34.71588516235352</v>
       </c>
       <c r="C10" t="n">
         <v>62.22407913208008</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.21598052978516</v>
+        <v>38.21596145629883</v>
       </c>
       <c r="C12" t="n">
         <v>68.11036682128906</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>34.97292327880859</v>
+        <v>34.97291946411133</v>
       </c>
       <c r="C15" t="n">
         <v>61.93980026245117</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.08236312866211</v>
+        <v>36.08235168457031</v>
       </c>
       <c r="C16" t="n">
         <v>63.90468215942383</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.75824356079102</v>
+        <v>41.75825500488281</v>
       </c>
       <c r="C18" t="n">
         <v>73.54515075683594</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>41.20278167724609</v>
+        <v>41.20277786254883</v>
       </c>
       <c r="C19" t="n">
         <v>72.56688690185547</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>42.21400833129883</v>
+        <v>42.21398544311523</v>
       </c>
       <c r="C20" t="n">
         <v>74.34782409667969</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>44.66866302490234</v>
+        <v>44.66865158081055</v>
       </c>
       <c r="C22" t="n">
         <v>78.24414825439453</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>39.97747802734375</v>
+        <v>39.97750091552734</v>
       </c>
       <c r="C24" t="n">
         <v>69.61538696289062</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>40.48645401000977</v>
+        <v>40.48644256591797</v>
       </c>
       <c r="C25" t="n">
         <v>70.50167083740234</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.244140625</v>
+        <v>38.24413681030273</v>
       </c>
       <c r="C26" t="n">
         <v>66.59699249267578</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>37.88115310668945</v>
+        <v>37.88114929199219</v>
       </c>
       <c r="C27" t="n">
         <v>65.55184173583984</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>38.2435417175293</v>
+        <v>38.24352645874023</v>
       </c>
       <c r="C28" t="n">
         <v>66.17893218994141</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>37.15636444091797</v>
+        <v>37.15637969970703</v>
       </c>
       <c r="C29" t="n">
         <v>64.29766082763672</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.71851348876953</v>
+        <v>37.71852111816406</v>
       </c>
       <c r="C30" t="n">
         <v>64.84949493408203</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>33.84260940551758</v>
+        <v>33.84260559082031</v>
       </c>
       <c r="C31" t="n">
         <v>58.18561935424805</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>35.06595993041992</v>
+        <v>35.06596755981445</v>
       </c>
       <c r="C33" t="n">
         <v>59.8662223815918</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>33.45467758178711</v>
+        <v>33.45469665527344</v>
       </c>
       <c r="C34" t="n">
         <v>57.11538314819336</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>31.49080467224121</v>
+        <v>31.49079322814941</v>
       </c>
       <c r="C35" t="n">
         <v>53.76254272460938</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>33.04460906982422</v>
+        <v>33.04458999633789</v>
       </c>
       <c r="C36" t="n">
         <v>55.9615364074707</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>28.40859413146973</v>
+        <v>28.40857315063477</v>
       </c>
       <c r="C37" t="n">
         <v>48.11036682128906</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>26.55713844299316</v>
+        <v>26.5571403503418</v>
       </c>
       <c r="C38" t="n">
         <v>44.97491455078125</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>22.68846702575684</v>
+        <v>22.68847465515137</v>
       </c>
       <c r="C39" t="n">
         <v>38.01003265380859</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>24.81458282470703</v>
+        <v>24.81457901000977</v>
       </c>
       <c r="C40" t="n">
         <v>41.57190704345703</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.74737548828125</v>
+        <v>28.74738311767578</v>
       </c>
       <c r="C41" t="n">
         <v>48.1605339050293</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.74631500244141</v>
+        <v>28.74631881713867</v>
       </c>
       <c r="C42" t="n">
         <v>47.74247360229492</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>30.25663566589355</v>
+        <v>30.25663185119629</v>
       </c>
       <c r="C43" t="n">
         <v>50.25083541870117</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>35.5024528503418</v>
+        <v>35.50248336791992</v>
       </c>
       <c r="C44" t="n">
         <v>58.96321105957031</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.56295776367188</v>
+        <v>36.56296157836914</v>
       </c>
       <c r="C45" t="n">
         <v>60.28428268432617</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>37.42506408691406</v>
+        <v>37.425048828125</v>
       </c>
       <c r="C46" t="n">
         <v>61.70568466186523</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>37.30841064453125</v>
+        <v>37.30842590332031</v>
       </c>
       <c r="C47" t="n">
         <v>61.51337814331055</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>39.52682876586914</v>
+        <v>39.52684020996094</v>
       </c>
       <c r="C48" t="n">
         <v>64.74916076660156</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>42.19632339477539</v>
+        <v>42.19631958007812</v>
       </c>
       <c r="C49" t="n">
         <v>69.1220703125</v>
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.17873764038086</v>
+        <v>41.1787223815918</v>
       </c>
       <c r="C51" t="n">
         <v>67.01505279541016</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.93582153320312</v>
+        <v>42.93581771850586</v>
       </c>
       <c r="C52" t="n">
         <v>69.87458038330078</v>
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.00335693359375</v>
+        <v>41.00336456298828</v>
       </c>
       <c r="C54" t="n">
         <v>66.31270599365234</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.83793258666992</v>
+        <v>40.83791732788086</v>
       </c>
       <c r="C55" t="n">
         <v>66.04515075683594</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>44.22429656982422</v>
+        <v>44.22428512573242</v>
       </c>
       <c r="C56" t="n">
         <v>71.52173614501953</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>40.86558532714844</v>
+        <v>40.86558151245117</v>
       </c>
       <c r="C57" t="n">
         <v>65.67726135253906</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>45.11080932617188</v>
+        <v>45.1108283996582</v>
       </c>
       <c r="C58" t="n">
         <v>72.5</v>
@@ -1655,7 +1667,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>43.96453857421875</v>
+        <v>43.96452713012695</v>
       </c>
       <c r="C60" t="n">
         <v>70.21739196777344</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>45.1790771484375</v>
+        <v>45.17908096313477</v>
       </c>
       <c r="C61" t="n">
         <v>72.15718841552734</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>46.02718353271484</v>
+        <v>46.02716445922852</v>
       </c>
       <c r="C62" t="n">
         <v>73.51170349121094</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>48.57390213012695</v>
+        <v>48.57390594482422</v>
       </c>
       <c r="C63" t="n">
         <v>77.11538696289062</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>49.24274444580078</v>
+        <v>49.24274826049805</v>
       </c>
       <c r="C64" t="n">
         <v>78.17726135253906</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>51.1966667175293</v>
+        <v>51.19667053222656</v>
       </c>
       <c r="C65" t="n">
         <v>81.27926635742188</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>49.99920654296875</v>
+        <v>49.99919891357422</v>
       </c>
       <c r="C66" t="n">
         <v>78.91304016113281</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.24819564819336</v>
+        <v>50.24820327758789</v>
       </c>
       <c r="C67" t="n">
         <v>79.30602264404297</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>46.1636962890625</v>
+        <v>46.16370391845703</v>
       </c>
       <c r="C68" t="n">
         <v>72.85953521728516</v>
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>42.14423751831055</v>
+        <v>42.14424514770508</v>
       </c>
       <c r="C71" t="n">
         <v>66.07023620605469</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>43.5269660949707</v>
+        <v>43.52696990966797</v>
       </c>
       <c r="C72" t="n">
         <v>67.75919342041016</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.8975715637207</v>
+        <v>43.89756011962891</v>
       </c>
       <c r="C73" t="n">
         <v>68.33612060546875</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.57236862182617</v>
+        <v>46.57236480712891</v>
       </c>
       <c r="C74" t="n">
         <v>72.5</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>47.36799621582031</v>
+        <v>47.36800003051758</v>
       </c>
       <c r="C75" t="n">
         <v>73.24414825439453</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>48.23857879638672</v>
+        <v>48.23856735229492</v>
       </c>
       <c r="C76" t="n">
         <v>74.59030151367188</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>48.31967544555664</v>
+        <v>48.31968688964844</v>
       </c>
       <c r="C77" t="n">
         <v>74.71572113037109</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.95919418334961</v>
+        <v>45.95917892456055</v>
       </c>
       <c r="C78" t="n">
         <v>70.57691955566406</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>48.78500366210938</v>
+        <v>48.78500747680664</v>
       </c>
       <c r="C79" t="n">
         <v>74.91638946533203</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>49.67250823974609</v>
+        <v>49.67251586914062</v>
       </c>
       <c r="C80" t="n">
         <v>76.27926635742188</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>50.73959732055664</v>
+        <v>50.73958969116211</v>
       </c>
       <c r="C81" t="n">
         <v>77.42475128173828</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.64097213745117</v>
+        <v>50.64098358154297</v>
       </c>
       <c r="C82" t="n">
         <v>77.27424621582031</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>47.99990463256836</v>
+        <v>47.99988174438477</v>
       </c>
       <c r="C83" t="n">
         <v>73.24414825439453</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.16593933105469</v>
+        <v>50.16593551635742</v>
       </c>
       <c r="C84" t="n">
         <v>76.04515075683594</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.21390914916992</v>
+        <v>51.21393585205078</v>
       </c>
       <c r="C85" t="n">
         <v>77.63378143310547</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>55.46108627319336</v>
+        <v>55.46108245849609</v>
       </c>
       <c r="C86" t="n">
         <v>84.07190704345703</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.71826934814453</v>
+        <v>57.7182502746582</v>
       </c>
       <c r="C87" t="n">
         <v>86.95652008056641</v>
@@ -2480,7 +2492,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>58.11231231689453</v>
+        <v>58.11230087280273</v>
       </c>
       <c r="C89" t="n">
         <v>87.55016326904297</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>61.54693984985352</v>
+        <v>61.54694366455078</v>
       </c>
       <c r="C90" t="n">
         <v>92.19899749755859</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.03343200683594</v>
+        <v>61.03342056274414</v>
       </c>
       <c r="C91" t="n">
         <v>91.42976379394531</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>65.54325103759766</v>
+        <v>65.54327392578125</v>
       </c>
       <c r="C92" t="n">
         <v>98.18561553955078</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>63.74510955810547</v>
+        <v>63.74509048461914</v>
       </c>
       <c r="C93" t="n">
         <v>94.966552734375</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>67.01712036132812</v>
+        <v>67.01711273193359</v>
       </c>
       <c r="C94" t="n">
         <v>99.84114074707031</v>
@@ -2683,7 +2695,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>75.29818725585938</v>
+        <v>75.29817962646484</v>
       </c>
       <c r="C96" t="n">
         <v>111.6304321289062</v>
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>72.29776000976562</v>
+        <v>72.29776763916016</v>
       </c>
       <c r="C98" t="n">
         <v>107.1822738647461</v>
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>77.01348114013672</v>
+        <v>77.01351928710938</v>
       </c>
       <c r="C100" t="n">
         <v>113.428092956543</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>78.960693359375</v>
+        <v>78.96067810058594</v>
       </c>
       <c r="C101" t="n">
         <v>116.2959899902344</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>81.42136383056641</v>
+        <v>81.42133331298828</v>
       </c>
       <c r="C102" t="n">
         <v>119.18896484375</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>81.81546783447266</v>
+        <v>81.81544494628906</v>
       </c>
       <c r="C103" t="n">
         <v>119.7658843994141</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>80.47319030761719</v>
+        <v>80.47319793701172</v>
       </c>
       <c r="C104" t="n">
         <v>117.8010025024414</v>
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>81.40693664550781</v>
+        <v>81.40694427490234</v>
       </c>
       <c r="C106" t="n">
         <v>118.461540222168</v>
@@ -3031,7 +3043,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>92.47870635986328</v>
+        <v>92.47872161865234</v>
       </c>
       <c r="C108" t="n">
         <v>133.8545074462891</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>94.92227172851562</v>
+        <v>94.92225646972656</v>
       </c>
       <c r="C109" t="n">
         <v>137.3912963867188</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>93.75534820556641</v>
+        <v>93.75540924072266</v>
       </c>
       <c r="C110" t="n">
         <v>135.7023468017578</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>98.02951049804688</v>
+        <v>98.02949523925781</v>
       </c>
       <c r="C111" t="n">
         <v>141.0117034912109</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>95.87882995605469</v>
+        <v>95.87885284423828</v>
       </c>
       <c r="C112" t="n">
         <v>137.9180603027344</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>90.90328216552734</v>
+        <v>90.90326690673828</v>
       </c>
       <c r="C113" t="n">
         <v>130.7608642578125</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>93.05157470703125</v>
+        <v>93.05158233642578</v>
       </c>
       <c r="C114" t="n">
         <v>133.0100402832031</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>90.25554656982422</v>
+        <v>90.25558471679688</v>
       </c>
       <c r="C115" t="n">
         <v>129.0133819580078</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>88.52415466308594</v>
+        <v>88.52416229248047</v>
       </c>
       <c r="C116" t="n">
         <v>126.538459777832</v>
@@ -3321,7 +3333,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>83.50345611572266</v>
+        <v>83.50344848632812</v>
       </c>
       <c r="C118" t="n">
         <v>118.5367889404297</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>92.59770202636719</v>
+        <v>92.59769439697266</v>
       </c>
       <c r="C119" t="n">
         <v>131.4464874267578</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>92.83258056640625</v>
+        <v>92.83259582519531</v>
       </c>
       <c r="C120" t="n">
         <v>130.9197387695312</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>89.31089019775391</v>
+        <v>89.31090545654297</v>
       </c>
       <c r="C121" t="n">
         <v>125.9531784057617</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>89.52433776855469</v>
+        <v>89.52436828613281</v>
       </c>
       <c r="C122" t="n">
         <v>126.2541809082031</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>93.67649841308594</v>
+        <v>93.67648315429688</v>
       </c>
       <c r="C123" t="n">
         <v>131.1622009277344</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>99.50477600097656</v>
+        <v>99.50475311279297</v>
       </c>
       <c r="C124" t="n">
         <v>139.3227386474609</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>99.95260620117188</v>
+        <v>99.95265197753906</v>
       </c>
       <c r="C125" t="n">
         <v>139.9498291015625</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>101.1832885742188</v>
+        <v>101.1832504272461</v>
       </c>
       <c r="C126" t="n">
         <v>140.7357788085938</v>
@@ -3611,7 +3623,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>107.2186737060547</v>
+        <v>107.2186660766602</v>
       </c>
       <c r="C128" t="n">
         <v>149.1304321289062</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>108.4190521240234</v>
+        <v>108.4190368652344</v>
       </c>
       <c r="C129" t="n">
         <v>149.8662261962891</v>
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,7 +3739,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>104.548454284668</v>
+        <v>104.5484390258789</v>
       </c>
       <c r="C132" t="n">
         <v>143.5953216552734</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>108.7063140869141</v>
+        <v>108.7062683105469</v>
       </c>
       <c r="C133" t="n">
         <v>149.3060150146484</v>
@@ -3814,7 +3826,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>114.1812286376953</v>
+        <v>114.1812133789062</v>
       </c>
       <c r="C135" t="n">
         <v>155.81103515625</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>117.2326202392578</v>
+        <v>117.2325744628906</v>
       </c>
       <c r="C136" t="n">
         <v>159.9749145507812</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>119.989875793457</v>
+        <v>119.9898529052734</v>
       </c>
       <c r="C137" t="n">
         <v>163.7374572753906</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>126.0320358276367</v>
+        <v>126.0320510864258</v>
       </c>
       <c r="C138" t="n">
         <v>170.9615325927734</v>
@@ -3959,7 +3971,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>123.9980239868164</v>
+        <v>123.9980163574219</v>
       </c>
       <c r="C140" t="n">
         <v>168.2023468017578</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>126.6640014648438</v>
+        <v>126.6639938354492</v>
       </c>
       <c r="C141" t="n">
         <v>170.8361206054688</v>
@@ -4046,7 +4058,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>142.7015380859375</v>
+        <v>142.7015686035156</v>
       </c>
       <c r="C143" t="n">
         <v>192.466552734375</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>151.4900665283203</v>
+        <v>151.4900207519531</v>
       </c>
       <c r="C144" t="n">
         <v>203.2943115234375</v>
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>147.6013793945312</v>
+        <v>147.6013641357422</v>
       </c>
       <c r="C147" t="n">
         <v>196.9147186279297</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>137.5799560546875</v>
+        <v>137.5799407958984</v>
       </c>
       <c r="C148" t="n">
         <v>183.5451507568359</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>121.8301849365234</v>
+        <v>121.8302154541016</v>
       </c>
       <c r="C149" t="n">
         <v>162.533447265625</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>124.4555130004883</v>
+        <v>124.4555053710938</v>
       </c>
       <c r="C150" t="n">
         <v>164.9080200195312</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>124.1336822509766</v>
+        <v>124.1337280273438</v>
       </c>
       <c r="C151" t="n">
         <v>164.4815979003906</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>133.9775695800781</v>
+        <v>133.9775390625</v>
       </c>
       <c r="C152" t="n">
         <v>177.5250854492188</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>133.9862060546875</v>
+        <v>133.9862365722656</v>
       </c>
       <c r="C153" t="n">
         <v>176.3545074462891</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>133.8528442382812</v>
+        <v>133.8528289794922</v>
       </c>
       <c r="C154" t="n">
         <v>176.1789245605469</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>120.8620758056641</v>
+        <v>120.8620681762695</v>
       </c>
       <c r="C155" t="n">
         <v>159.0802612304688</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>132.9825286865234</v>
+        <v>132.9824829101562</v>
       </c>
       <c r="C156" t="n">
         <v>173.8461608886719</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>121.8665466308594</v>
+        <v>121.8664855957031</v>
       </c>
       <c r="C157" t="n">
         <v>159.3143768310547</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>128.1088409423828</v>
+        <v>128.10888671875</v>
       </c>
       <c r="C158" t="n">
         <v>167.4749145507812</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>133.5605926513672</v>
+        <v>133.560546875</v>
       </c>
       <c r="C159" t="n">
         <v>173.4030151367188</v>
@@ -4568,7 +4580,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>103.7603302001953</v>
+        <v>103.7603530883789</v>
       </c>
       <c r="C162" t="n">
         <v>133.5702362060547</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>112.5872650146484</v>
+        <v>112.5872573852539</v>
       </c>
       <c r="C163" t="n">
         <v>144.93310546875</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>113.4835968017578</v>
+        <v>113.4836273193359</v>
       </c>
       <c r="C164" t="n">
         <v>146.0869598388672</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>106.0010299682617</v>
+        <v>106.0010604858398</v>
       </c>
       <c r="C165" t="n">
         <v>135.2173919677734</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>107.7576904296875</v>
+        <v>107.7576751708984</v>
       </c>
       <c r="C166" t="n">
         <v>137.4581909179688</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>108.1444091796875</v>
+        <v>108.1444244384766</v>
       </c>
       <c r="C167" t="n">
         <v>137.9515075683594</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>112.2408828735352</v>
+        <v>112.2408905029297</v>
       </c>
       <c r="C168" t="n">
         <v>141.9481658935547</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>116.6374053955078</v>
+        <v>116.6374282836914</v>
       </c>
       <c r="C169" t="n">
         <v>147.5083618164062</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>104.8956756591797</v>
+        <v>104.8956680297852</v>
       </c>
       <c r="C170" t="n">
         <v>132.6588592529297</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>99.56129455566406</v>
+        <v>99.56128692626953</v>
       </c>
       <c r="C171" t="n">
         <v>124.7826080322266</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>91.06883239746094</v>
+        <v>91.06881713867188</v>
       </c>
       <c r="C172" t="n">
         <v>114.1387939453125</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>101.3491668701172</v>
+        <v>101.3491744995117</v>
       </c>
       <c r="C173" t="n">
         <v>127.0234146118164</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>105.3996887207031</v>
+        <v>105.3996810913086</v>
       </c>
       <c r="C174" t="n">
         <v>130.8026733398438</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>105.0965042114258</v>
+        <v>105.0965118408203</v>
       </c>
       <c r="C175" t="n">
         <v>130.4264221191406</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>101.3774566650391</v>
+        <v>101.3774642944336</v>
       </c>
       <c r="C176" t="n">
         <v>125.81103515625</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>110.8326110839844</v>
+        <v>110.8326034545898</v>
       </c>
       <c r="C177" t="n">
         <v>136.3043518066406</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>108.9017868041992</v>
+        <v>108.9017639160156</v>
       </c>
       <c r="C178" t="n">
         <v>133.9297637939453</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>108.7522125244141</v>
+        <v>108.7522201538086</v>
       </c>
       <c r="C179" t="n">
         <v>133.7458190917969</v>
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>118.4500579833984</v>
+        <v>118.4500427246094</v>
       </c>
       <c r="C180" t="n">
         <v>144.4230804443359</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>119.8627166748047</v>
+        <v>119.8626937866211</v>
       </c>
       <c r="C181" t="n">
         <v>146.1454925537109</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>120.459342956543</v>
+        <v>120.4592742919922</v>
       </c>
       <c r="C182" t="n">
         <v>146.8729095458984</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>121.0370941162109</v>
+        <v>121.0370864868164</v>
       </c>
       <c r="C183" t="n">
         <v>146.3712310791016</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>133.2196197509766</v>
+        <v>133.2196502685547</v>
       </c>
       <c r="C184" t="n">
         <v>161.1036834716797</v>
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>136.3032836914062</v>
+        <v>136.3033142089844</v>
       </c>
       <c r="C185" t="n">
         <v>164.8327789306641</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>141.4156036376953</v>
+        <v>141.4156188964844</v>
       </c>
       <c r="C186" t="n">
         <v>169.7658843994141</v>
@@ -5351,7 +5363,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>137.8635406494141</v>
+        <v>137.8635559082031</v>
       </c>
       <c r="C188" t="n">
         <v>165.5016784667969</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>136.6701202392578</v>
+        <v>136.6701049804688</v>
       </c>
       <c r="C189" t="n">
         <v>162.8260803222656</v>
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>125.3991012573242</v>
+        <v>125.3990707397461</v>
       </c>
       <c r="C191" t="n">
         <v>149.3979949951172</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>120.306640625</v>
+        <v>120.3066024780273</v>
       </c>
       <c r="C192" t="n">
         <v>142.1739196777344</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>125.6767044067383</v>
+        <v>125.6767272949219</v>
       </c>
       <c r="C193" t="n">
         <v>148.5200653076172</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>117.46240234375</v>
+        <v>117.4624252319336</v>
       </c>
       <c r="C194" t="n">
         <v>138.8127136230469</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>106.1894454956055</v>
+        <v>106.1894378662109</v>
       </c>
       <c r="C195" t="n">
         <v>124.2892990112305</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>106.353759765625</v>
+        <v>106.3537445068359</v>
       </c>
       <c r="C196" t="n">
         <v>124.4816055297852</v>
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>103.0248413085938</v>
+        <v>103.0248336791992</v>
       </c>
       <c r="C197" t="n">
         <v>120.5852813720703</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>107.7243804931641</v>
+        <v>107.7243957519531</v>
       </c>
       <c r="C198" t="n">
         <v>124.8244171142578</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>93.37940979003906</v>
+        <v>93.37939453125</v>
       </c>
       <c r="C199" t="n">
         <v>108.2023391723633</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>103.3588333129883</v>
+        <v>103.3588180541992</v>
       </c>
       <c r="C200" t="n">
         <v>119.7658843994141</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>90.64906311035156</v>
+        <v>90.6490478515625</v>
       </c>
       <c r="C201" t="n">
         <v>103.9715728759766</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>80.55263519287109</v>
+        <v>80.55264282226562</v>
       </c>
       <c r="C202" t="n">
         <v>92.39130401611328</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>91.69879150390625</v>
+        <v>91.69877624511719</v>
       </c>
       <c r="C203" t="n">
         <v>105.1755828857422</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>92.90526580810547</v>
+        <v>92.90525817871094</v>
       </c>
       <c r="C204" t="n">
         <v>105.3260879516602</v>
@@ -5873,7 +5885,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>84.87367248535156</v>
+        <v>84.87368011474609</v>
       </c>
       <c r="C206" t="n">
         <v>96.22073364257812</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>80.51238250732422</v>
+        <v>80.51239013671875</v>
       </c>
       <c r="C207" t="n">
         <v>90.08361053466797</v>
@@ -5960,11 +5972,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>78.54703521728516</v>
+        <v>78.54702758789062</v>
       </c>
       <c r="C208" t="n">
         <v>87.88461303710938</v>
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>79.37651824951172</v>
+        <v>79.37650299072266</v>
       </c>
       <c r="C209" t="n">
         <v>88.81270599365234</v>
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>70.78898620605469</v>
+        <v>70.78900146484375</v>
       </c>
       <c r="C210" t="n">
         <v>78.01839447021484</v>
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>75.93260955810547</v>
+        <v>75.93259429931641</v>
       </c>
       <c r="C211" t="n">
         <v>83.68729400634766</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>84.58872222900391</v>
+        <v>84.58871459960938</v>
       </c>
       <c r="C212" t="n">
         <v>93.22742462158203</v>
@@ -6103,11 +6115,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>82.13471984863281</v>
+        <v>82.13470458984375</v>
       </c>
       <c r="C213" t="n">
         <v>89.18896484375</v>
@@ -6130,7 +6142,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6157,7 +6169,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6184,7 +6196,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6211,7 +6223,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>73.79167175292969</v>
+        <v>73.79169464111328</v>
       </c>
       <c r="C218" t="n">
         <v>78.88796234130859</v>
@@ -6265,11 +6277,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>73.24427795410156</v>
+        <v>73.24429321289062</v>
       </c>
       <c r="C219" t="n">
         <v>77.02341461181641</v>
@@ -6292,7 +6304,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6319,7 +6331,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6346,11 +6358,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>95.88802337646484</v>
+        <v>95.88803100585938</v>
       </c>
       <c r="C222" t="n">
         <v>100.1399993896484</v>
@@ -6373,11 +6385,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>97.85099029541016</v>
+        <v>97.85098266601562</v>
       </c>
       <c r="C223" t="n">
         <v>102.1900024414062</v>
@@ -6400,11 +6412,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>122.1341934204102</v>
+        <v>122.1341857910156</v>
       </c>
       <c r="C224" t="n">
         <v>127.5500030517578</v>
@@ -6429,7 +6441,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6458,11 +6470,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>131.6012878417969</v>
+        <v>131.6013031005859</v>
       </c>
       <c r="C226" t="n">
         <v>136.6999969482422</v>
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6516,7 +6528,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6545,7 +6557,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6574,7 +6586,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6603,11 +6615,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>150.8690338134766</v>
+        <v>150.8690185546875</v>
       </c>
       <c r="C231" t="n">
         <v>155.1199951171875</v>
@@ -6632,7 +6644,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6661,11 +6673,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>135.1032562255859</v>
+        <v>135.103271484375</v>
       </c>
       <c r="C233" t="n">
         <v>138.9100036621094</v>
@@ -6690,7 +6702,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6719,7 +6731,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6777,11 +6789,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>152.7110290527344</v>
+        <v>152.7110137939453</v>
       </c>
       <c r="C237" t="n">
         <v>155.5299987792969</v>
@@ -6806,11 +6818,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>152.3673553466797</v>
+        <v>152.3673400878906</v>
       </c>
       <c r="C238" t="n">
         <v>155.1799926757812</v>
@@ -6835,11 +6847,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>163.4822082519531</v>
+        <v>163.4821929931641</v>
       </c>
       <c r="C239" t="n">
         <v>166.5</v>
@@ -6864,11 +6876,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>169.657470703125</v>
+        <v>169.6574859619141</v>
       </c>
       <c r="C240" t="n">
         <v>172.0500030517578</v>
@@ -6893,7 +6905,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6922,7 +6934,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6951,11 +6963,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>163.7525787353516</v>
+        <v>163.7525634765625</v>
       </c>
       <c r="C243" t="n">
         <v>165.3200073242188</v>
@@ -6980,11 +6992,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>143.8530426025391</v>
+        <v>143.85302734375</v>
       </c>
       <c r="C244" t="n">
         <v>145.2299957275391</v>
@@ -7009,7 +7021,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7096,7 +7108,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7154,32 +7166,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>170.3000030517578</v>
+        <v>167.5200042724609</v>
       </c>
       <c r="C250" t="n">
-        <v>170.3000030517578</v>
+        <v>167.5200042724609</v>
       </c>
       <c r="D250" t="n">
-        <v>47801000</v>
+        <v>50231700</v>
       </c>
       <c r="E250" t="n">
         <v>5.630000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>30.24866839285218</v>
+        <v>29.75488530594333</v>
       </c>
       <c r="G250" t="n">
         <v>515722417</v>
       </c>
       <c r="H250" t="n">
-        <v>87827529188.95992</v>
+        <v>86393821499.24388</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09268745826109785</v>
+        <v>0.0974006526460532</v>
       </c>
     </row>
   </sheetData>
@@ -7211,75 +7223,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7516,7 +7528,7 @@
       <c r="I7" t="n">
         <v>3.770903010033445</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="K7" t="n">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7562,7 +7574,7 @@
       <c r="I8" t="n">
         <v>4.230769230769232</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="K8" t="n">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7608,7 +7620,7 @@
       <c r="I9" t="n">
         <v>4.581939799331104</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="K9" t="n">
@@ -7621,13 +7633,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7654,7 +7666,7 @@
       <c r="I10" t="n">
         <v>4.732441471571907</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="K10" t="n">
@@ -7667,13 +7679,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7700,7 +7712,7 @@
       <c r="I11" t="n">
         <v>4.71571906354515</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="K11" t="n">
@@ -7713,13 +7725,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7746,7 +7758,7 @@
       <c r="I12" t="n">
         <v>4.882943143812709</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K12" t="n">
@@ -7759,13 +7771,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7792,7 +7804,7 @@
       <c r="I13" t="n">
         <v>4.933110367892977</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K13" t="n">
@@ -7805,13 +7817,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7838,7 +7850,7 @@
       <c r="I14" t="n">
         <v>4.924749163879599</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7851,13 +7863,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7884,7 +7896,7 @@
       <c r="I15" t="n">
         <v>4.983277591973245</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K15" t="n">
@@ -7897,13 +7909,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7930,7 +7942,7 @@
       <c r="I16" t="n">
         <v>5.066889632107024</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K16" t="n">
@@ -7943,13 +7955,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7976,7 +7988,7 @@
       <c r="I17" t="n">
         <v>5.117056856187292</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K17" t="n">
@@ -7989,13 +8001,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8022,7 +8034,7 @@
       <c r="I18" t="n">
         <v>5.225752508361205</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K18" t="n">
@@ -8035,13 +8047,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="I19" t="n">
         <v>5.275919732441471</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="K19" t="n">
@@ -8081,13 +8093,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8114,7 +8126,7 @@
       <c r="I20" t="n">
         <v>5.292642140468228</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K20" t="n">
@@ -8127,13 +8139,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8160,7 +8172,7 @@
       <c r="I21" t="n">
         <v>5.334448160535118</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="K21" t="n">
@@ -8173,13 +8185,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8206,7 +8218,7 @@
       <c r="I22" t="n">
         <v>5.443143812709031</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K22" t="n">
@@ -8219,13 +8231,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8252,7 +8264,7 @@
       <c r="I23" t="n">
         <v>5.618729096989967</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="K23" t="n">
@@ -8265,13 +8277,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8298,7 +8310,7 @@
       <c r="I24" t="n">
         <v>5.76923076923077</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K24" t="n">
@@ -8311,13 +8323,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8344,7 +8356,7 @@
       <c r="I25" t="n">
         <v>5.936454849498328</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -8357,13 +8369,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8390,7 +8402,7 @@
       <c r="I26" t="n">
         <v>6.103678929765886</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K26" t="n">
@@ -8403,13 +8415,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8436,7 +8448,7 @@
       <c r="I27" t="n">
         <v>6.262541806020067</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K27" t="n">
@@ -8449,13 +8461,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8482,7 +8494,7 @@
       <c r="I28" t="n">
         <v>6.312709030100335</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K28" t="n">
@@ -8495,13 +8507,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8528,7 +8540,7 @@
       <c r="I29" t="n">
         <v>6.404682274247492</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8541,13 +8553,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8574,7 +8586,7 @@
       <c r="I30" t="n">
         <v>6.463210702341137</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K30" t="n">
@@ -8587,13 +8599,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8620,7 +8632,7 @@
       <c r="I31" t="n">
         <v>6.337792642140469</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K31" t="n">
@@ -8633,13 +8645,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8666,7 +8678,7 @@
       <c r="I32" t="n">
         <v>6.505016722408026</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="K32" t="n">
@@ -8679,13 +8691,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8712,7 +8724,7 @@
       <c r="I33" t="n">
         <v>6.555183946488294</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K33" t="n">
@@ -8725,13 +8737,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8758,7 +8770,7 @@
       <c r="I34" t="n">
         <v>6.638795986622074</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K34" t="n">
@@ -8771,13 +8783,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8804,7 +8816,7 @@
       <c r="I35" t="n">
         <v>6.822742474916389</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K35" t="n">
@@ -8817,13 +8829,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8850,7 +8862,7 @@
       <c r="I36" t="n">
         <v>6.914715719063546</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8863,13 +8875,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8896,7 +8908,7 @@
       <c r="I37" t="n">
         <v>7.332775919732442</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K37" t="n">
@@ -8909,13 +8921,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8942,7 +8954,7 @@
       <c r="I38" t="n">
         <v>7.483277591973245</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K38" t="n">
@@ -8955,13 +8967,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8988,7 +9000,7 @@
       <c r="I39" t="n">
         <v>6.622073578595318</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K39" t="n">
@@ -9001,13 +9013,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9034,7 +9046,7 @@
       <c r="I40" t="n">
         <v>5.635451505016723</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K40" t="n">
@@ -9047,13 +9059,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9080,7 +9092,7 @@
       <c r="I41" t="n">
         <v>6.045150501672241</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9093,13 +9105,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9126,7 +9138,7 @@
       <c r="I42" t="n">
         <v>6.25418060200669</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K42" t="n">
@@ -9139,13 +9151,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9172,7 +9184,7 @@
       <c r="I43" t="n">
         <v>7.441471571906355</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K43" t="n">
@@ -9185,13 +9197,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9218,7 +9230,7 @@
       <c r="I44" t="n">
         <v>7.884615384615385</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9231,13 +9243,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9264,7 +9276,7 @@
       <c r="I45" t="n">
         <v>6.923076923076923</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9277,13 +9289,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9310,7 +9322,7 @@
       <c r="I46" t="n">
         <v>7.040133779264215</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K46" t="n">
@@ -9323,13 +9335,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9356,7 +9368,7 @@
       <c r="I47" t="n">
         <v>6.530100334448161</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K47" t="n">
@@ -9369,13 +9381,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9402,7 +9414,7 @@
       <c r="I48" t="n">
         <v>7.123745819397993</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K48" t="n">
@@ -9415,13 +9427,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="I49" t="n">
         <v>7.374581939799332</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K49" t="n">
@@ -9461,13 +9473,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9494,7 +9506,7 @@
       <c r="I50" t="n">
         <v>7.132107023411372</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K50" t="n">
@@ -9507,13 +9519,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9540,7 +9552,7 @@
       <c r="I51" t="n">
         <v>7.734113712374583</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K51" t="n">
@@ -9553,13 +9565,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9586,7 +9598,7 @@
       <c r="I52" t="n">
         <v>8.193979933110368</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K52" t="n">
@@ -9599,13 +9611,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="I53" t="n">
         <v>8.503344481605351</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K53" t="n">
@@ -9645,13 +9657,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9678,7 +9690,7 @@
       <c r="I54" t="n">
         <v>8.520066889632107</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K54" t="n">
@@ -9691,13 +9703,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9724,7 +9736,7 @@
       <c r="I55" t="n">
         <v>8.46153846153846</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K55" t="n">
@@ -9737,13 +9749,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9770,7 +9782,7 @@
       <c r="I56" t="n">
         <v>8.035117056856187</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K56" t="n">
@@ -9783,13 +9795,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9816,7 +9828,7 @@
       <c r="I57" t="n">
         <v>5.986622073578595</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9829,13 +9841,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9862,7 +9874,7 @@
       <c r="I58" t="n">
         <v>9.598662207357858</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K58" t="n">
@@ -9875,13 +9887,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9908,7 +9920,7 @@
       <c r="I59" t="n">
         <v>8.511705685618729</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="K59" t="n">
@@ -9921,13 +9933,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="I60" t="n">
         <v>8.093645484949832</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K60" t="n">
@@ -9967,13 +9979,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10000,7 +10012,7 @@
       <c r="I61" t="n">
         <v>-2.349498327759199</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K61" t="n">
@@ -10013,13 +10025,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10046,7 +10058,7 @@
       <c r="I62" t="n">
         <v>-11.1371237458194</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K62" t="n">
@@ -10059,13 +10071,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10092,7 +10104,7 @@
       <c r="I63" t="n">
         <v>-10.56020066889633</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="K63" t="n">
@@ -10105,13 +10117,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10138,7 +10150,7 @@
       <c r="I64" t="n">
         <v>-10.36177257525084</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K64" t="n">
@@ -10151,13 +10163,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10184,7 +10196,7 @@
       <c r="I65" t="n">
         <v>2.034314381270902</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K65" t="n">
@@ -10197,13 +10209,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10230,7 +10242,7 @@
       <c r="I66" t="n">
         <v>7.641404682274247</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K66" t="n">
@@ -10243,13 +10255,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10276,7 +10288,7 @@
       <c r="I67" t="n">
         <v>7.550000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K67" t="n">
@@ -10289,13 +10301,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10322,7 +10334,7 @@
       <c r="I68" t="n">
         <v>7.92</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="K68" t="n">
@@ -10335,13 +10347,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10368,7 +10380,7 @@
       <c r="I69" t="n">
         <v>7.19</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="K69" t="n">
@@ -10381,13 +10393,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10414,7 +10426,7 @@
       <c r="I70" t="n">
         <v>6.260000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K70" t="n">
@@ -10427,13 +10439,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10460,7 +10472,7 @@
       <c r="I71" t="n">
         <v>6</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K71" t="n">
@@ -10473,13 +10485,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10506,7 +10518,7 @@
       <c r="I72" t="n">
         <v>5.19</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="K72" t="n">
@@ -10519,13 +10531,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10552,7 +10564,7 @@
       <c r="I73" t="n">
         <v>5.630000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="K73" t="n">
@@ -10589,52 +10601,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C2" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="C3" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40225</v>
       </c>
       <c r="C4" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C5" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C6" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40590</v>
       </c>
       <c r="C8" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="C12" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C15" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41319</v>
       </c>
       <c r="C16" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C18" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C19" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="C20" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C21" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C22" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C23" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C24" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C25" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C27" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="C29" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C30" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C31" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C34" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C35" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C36" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C37" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C44" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C45" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C46" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C47" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C48" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C50" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C51" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C52" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C53" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C55" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="C56" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C57" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C58" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C59" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="C60" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C61" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C62" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C63" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C64" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="C65" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="C66" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C67" t="n">
@@ -12743,10 +12755,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C68" t="n">
@@ -12775,10 +12787,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C69" t="n">
@@ -12807,10 +12819,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="C70" t="n">
@@ -12857,12 +12869,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MMM.xlsx
+++ b/salidas/empresas/MMM.xlsx
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>34.89449691772461</v>
+        <v>34.8945198059082</v>
       </c>
       <c r="C4" t="n">
         <v>63.28595352172852</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>39.38480758666992</v>
+        <v>39.38482666015625</v>
       </c>
       <c r="C5" t="n">
         <v>71.42976379394531</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>38.77438735961914</v>
+        <v>38.77439498901367</v>
       </c>
       <c r="C6" t="n">
         <v>69.94983673095703</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>37.43495178222656</v>
+        <v>37.43494415283203</v>
       </c>
       <c r="C7" t="n">
         <v>67.533447265625</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>34.71588516235352</v>
+        <v>34.71587371826172</v>
       </c>
       <c r="C10" t="n">
         <v>62.22407913208008</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.77774429321289</v>
+        <v>36.77775192260742</v>
       </c>
       <c r="C11" t="n">
         <v>65.91973114013672</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.21596145629883</v>
+        <v>38.21595764160156</v>
       </c>
       <c r="C12" t="n">
         <v>68.11036682128906</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>34.85693359375</v>
+        <v>34.8569221496582</v>
       </c>
       <c r="C14" t="n">
         <v>62.12374496459961</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>34.97291946411133</v>
+        <v>34.97293853759766</v>
       </c>
       <c r="C15" t="n">
         <v>61.93980026245117</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>39.07545471191406</v>
+        <v>39.07545852661133</v>
       </c>
       <c r="C17" t="n">
         <v>69.2056884765625</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.75825500488281</v>
+        <v>41.75823593139648</v>
       </c>
       <c r="C18" t="n">
         <v>73.54515075683594</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>41.20277786254883</v>
+        <v>41.20278930664062</v>
       </c>
       <c r="C19" t="n">
         <v>72.56688690185547</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>42.21398544311523</v>
+        <v>42.21399688720703</v>
       </c>
       <c r="C20" t="n">
         <v>74.34782409667969</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>43.43238067626953</v>
+        <v>43.43238830566406</v>
       </c>
       <c r="C21" t="n">
         <v>76.07859802246094</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>44.66865158081055</v>
+        <v>44.66865539550781</v>
       </c>
       <c r="C22" t="n">
         <v>78.24414825439453</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>41.22232437133789</v>
+        <v>41.22233581542969</v>
       </c>
       <c r="C23" t="n">
         <v>72.20735931396484</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>39.97750091552734</v>
+        <v>39.97748565673828</v>
       </c>
       <c r="C24" t="n">
         <v>69.61538696289062</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>40.48644256591797</v>
+        <v>40.4864387512207</v>
       </c>
       <c r="C25" t="n">
         <v>70.50167083740234</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.24413681030273</v>
+        <v>38.2441291809082</v>
       </c>
       <c r="C26" t="n">
         <v>66.59699249267578</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>37.88114929199219</v>
+        <v>37.88116073608398</v>
       </c>
       <c r="C27" t="n">
         <v>65.55184173583984</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>37.15637969970703</v>
+        <v>37.15637588500977</v>
       </c>
       <c r="C29" t="n">
         <v>64.29766082763672</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.71852111816406</v>
+        <v>37.71853637695312</v>
       </c>
       <c r="C30" t="n">
         <v>64.84949493408203</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>33.84260559082031</v>
+        <v>33.84260940551758</v>
       </c>
       <c r="C31" t="n">
         <v>58.18561935424805</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>34.23166275024414</v>
+        <v>34.23165130615234</v>
       </c>
       <c r="C32" t="n">
         <v>58.85451507568359</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>35.06596755981445</v>
+        <v>35.06595611572266</v>
       </c>
       <c r="C33" t="n">
         <v>59.8662223815918</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>33.45469665527344</v>
+        <v>33.4547004699707</v>
       </c>
       <c r="C34" t="n">
         <v>57.11538314819336</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>31.49079322814941</v>
+        <v>31.49080467224121</v>
       </c>
       <c r="C35" t="n">
         <v>53.76254272460938</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>33.04458999633789</v>
+        <v>33.04461288452148</v>
       </c>
       <c r="C36" t="n">
         <v>55.9615364074707</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>28.40857315063477</v>
+        <v>28.4085750579834</v>
       </c>
       <c r="C37" t="n">
         <v>48.11036682128906</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>26.5571403503418</v>
+        <v>26.55713081359863</v>
       </c>
       <c r="C38" t="n">
         <v>44.97491455078125</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>22.68847465515137</v>
+        <v>22.68847846984863</v>
       </c>
       <c r="C39" t="n">
         <v>38.01003265380859</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>24.81457901000977</v>
+        <v>24.8145751953125</v>
       </c>
       <c r="C40" t="n">
         <v>41.57190704345703</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>28.74738311767578</v>
+        <v>28.74737548828125</v>
       </c>
       <c r="C41" t="n">
         <v>48.1605339050293</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>28.74631881713867</v>
+        <v>28.7463207244873</v>
       </c>
       <c r="C42" t="n">
         <v>47.74247360229492</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>35.50248336791992</v>
+        <v>35.50246810913086</v>
       </c>
       <c r="C44" t="n">
         <v>58.96321105957031</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.56296157836914</v>
+        <v>36.56295776367188</v>
       </c>
       <c r="C45" t="n">
         <v>60.28428268432617</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>37.425048828125</v>
+        <v>37.42504501342773</v>
       </c>
       <c r="C46" t="n">
         <v>61.70568466186523</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>37.30842590332031</v>
+        <v>37.30840682983398</v>
       </c>
       <c r="C47" t="n">
         <v>61.51337814331055</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>42.19631958007812</v>
+        <v>42.19630813598633</v>
       </c>
       <c r="C49" t="n">
         <v>69.1220703125</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>41.08362197875977</v>
+        <v>41.08361053466797</v>
       </c>
       <c r="C50" t="n">
         <v>67.29933166503906</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.1787223815918</v>
+        <v>41.17873001098633</v>
       </c>
       <c r="C51" t="n">
         <v>67.01505279541016</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.93581771850586</v>
+        <v>42.93582153320312</v>
       </c>
       <c r="C52" t="n">
         <v>69.87458038330078</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>45.5560417175293</v>
+        <v>45.55603790283203</v>
       </c>
       <c r="C53" t="n">
         <v>74.1387939453125</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.00336456298828</v>
+        <v>41.00337219238281</v>
       </c>
       <c r="C54" t="n">
         <v>66.31270599365234</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.83791732788086</v>
+        <v>40.83793640136719</v>
       </c>
       <c r="C55" t="n">
         <v>66.04515075683594</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>44.22428512573242</v>
+        <v>44.22429656982422</v>
       </c>
       <c r="C56" t="n">
         <v>71.52173614501953</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>45.1108283996582</v>
+        <v>45.11082077026367</v>
       </c>
       <c r="C58" t="n">
         <v>72.5</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>43.81540298461914</v>
+        <v>43.81538772583008</v>
       </c>
       <c r="C59" t="n">
         <v>70.41806030273438</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>43.96452713012695</v>
+        <v>43.96453094482422</v>
       </c>
       <c r="C60" t="n">
         <v>70.21739196777344</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>45.17908096313477</v>
+        <v>45.1790771484375</v>
       </c>
       <c r="C61" t="n">
         <v>72.15718841552734</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>48.57390594482422</v>
+        <v>48.57391738891602</v>
       </c>
       <c r="C63" t="n">
         <v>77.11538696289062</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>49.24274826049805</v>
+        <v>49.24276733398438</v>
       </c>
       <c r="C64" t="n">
         <v>78.17726135253906</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>51.19667053222656</v>
+        <v>51.19664001464844</v>
       </c>
       <c r="C65" t="n">
         <v>81.27926635742188</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>49.99919891357422</v>
+        <v>49.99918746948242</v>
       </c>
       <c r="C66" t="n">
         <v>78.91304016113281</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.24820327758789</v>
+        <v>50.24819183349609</v>
       </c>
       <c r="C67" t="n">
         <v>79.30602264404297</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>46.16370391845703</v>
+        <v>46.1637077331543</v>
       </c>
       <c r="C68" t="n">
         <v>72.85953521728516</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>44.25625228881836</v>
+        <v>44.25625991821289</v>
       </c>
       <c r="C69" t="n">
         <v>69.38127136230469</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>38.28822708129883</v>
+        <v>38.28822326660156</v>
       </c>
       <c r="C70" t="n">
         <v>60.02508544921875</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>42.14424514770508</v>
+        <v>42.14425277709961</v>
       </c>
       <c r="C71" t="n">
         <v>66.07023620605469</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>43.89756011962891</v>
+        <v>43.8975830078125</v>
       </c>
       <c r="C73" t="n">
         <v>68.33612060546875</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.57236480712891</v>
+        <v>46.57236099243164</v>
       </c>
       <c r="C74" t="n">
         <v>72.5</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>48.23856735229492</v>
+        <v>48.23857498168945</v>
       </c>
       <c r="C76" t="n">
         <v>74.59030151367188</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>48.31968688964844</v>
+        <v>48.31967544555664</v>
       </c>
       <c r="C77" t="n">
         <v>74.71572113037109</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.95917892456055</v>
+        <v>45.95916748046875</v>
       </c>
       <c r="C78" t="n">
         <v>70.57691955566406</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>48.78500747680664</v>
+        <v>48.78502655029297</v>
       </c>
       <c r="C79" t="n">
         <v>74.91638946533203</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>49.67251586914062</v>
+        <v>49.67250823974609</v>
       </c>
       <c r="C80" t="n">
         <v>76.27926635742188</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>50.73958969116211</v>
+        <v>50.73960113525391</v>
       </c>
       <c r="C81" t="n">
         <v>77.42475128173828</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.64098358154297</v>
+        <v>50.6409797668457</v>
       </c>
       <c r="C82" t="n">
         <v>77.27424621582031</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>47.99988174438477</v>
+        <v>47.99989700317383</v>
       </c>
       <c r="C83" t="n">
         <v>73.24414825439453</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>50.16593551635742</v>
+        <v>50.16592788696289</v>
       </c>
       <c r="C84" t="n">
         <v>76.04515075683594</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.21393585205078</v>
+        <v>51.21393966674805</v>
       </c>
       <c r="C85" t="n">
         <v>77.63378143310547</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>55.46108245849609</v>
+        <v>55.46106719970703</v>
       </c>
       <c r="C86" t="n">
         <v>84.07190704345703</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.7182502746582</v>
+        <v>57.71825408935547</v>
       </c>
       <c r="C87" t="n">
         <v>86.95652008056641</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>59.00028228759766</v>
+        <v>59.00030136108398</v>
       </c>
       <c r="C88" t="n">
         <v>88.88796234130859</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>58.11230087280273</v>
+        <v>58.1123046875</v>
       </c>
       <c r="C89" t="n">
         <v>87.55016326904297</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>61.54694366455078</v>
+        <v>61.54695129394531</v>
       </c>
       <c r="C90" t="n">
         <v>92.19899749755859</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.03342056274414</v>
+        <v>61.03346252441406</v>
       </c>
       <c r="C91" t="n">
         <v>91.42976379394531</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>65.54327392578125</v>
+        <v>65.54326629638672</v>
       </c>
       <c r="C92" t="n">
         <v>98.18561553955078</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>63.74509048461914</v>
+        <v>63.7451057434082</v>
       </c>
       <c r="C93" t="n">
         <v>94.966552734375</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>67.01711273193359</v>
+        <v>67.01710510253906</v>
       </c>
       <c r="C94" t="n">
         <v>99.84114074707031</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>70.63147735595703</v>
+        <v>70.63148498535156</v>
       </c>
       <c r="C95" t="n">
         <v>105.2257537841797</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>75.29817962646484</v>
+        <v>75.29818725585938</v>
       </c>
       <c r="C96" t="n">
         <v>111.6304321289062</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>79.09947204589844</v>
+        <v>79.09944915771484</v>
       </c>
       <c r="C97" t="n">
         <v>117.2658843994141</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>72.29776763916016</v>
+        <v>72.29779815673828</v>
       </c>
       <c r="C98" t="n">
         <v>107.1822738647461</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>76.48553466796875</v>
+        <v>76.48555755615234</v>
       </c>
       <c r="C99" t="n">
         <v>112.650505065918</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>77.01351928710938</v>
+        <v>77.01349639892578</v>
       </c>
       <c r="C100" t="n">
         <v>113.428092956543</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>78.96067810058594</v>
+        <v>78.96068572998047</v>
       </c>
       <c r="C101" t="n">
         <v>116.2959899902344</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>81.42133331298828</v>
+        <v>81.42135620117188</v>
       </c>
       <c r="C102" t="n">
         <v>119.18896484375</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>81.81544494628906</v>
+        <v>81.81545257568359</v>
       </c>
       <c r="C103" t="n">
         <v>119.7658843994141</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>82.73998260498047</v>
+        <v>82.73997497558594</v>
       </c>
       <c r="C105" t="n">
         <v>120.4013366699219</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>88.35364532470703</v>
+        <v>88.3536376953125</v>
       </c>
       <c r="C107" t="n">
         <v>128.5702362060547</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>92.47872161865234</v>
+        <v>92.47873687744141</v>
       </c>
       <c r="C108" t="n">
         <v>133.8545074462891</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>94.92225646972656</v>
+        <v>94.92230224609375</v>
       </c>
       <c r="C109" t="n">
         <v>137.3912963867188</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>93.75540924072266</v>
+        <v>93.75536346435547</v>
       </c>
       <c r="C110" t="n">
         <v>135.7023468017578</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>98.02949523925781</v>
+        <v>98.02950286865234</v>
       </c>
       <c r="C111" t="n">
         <v>141.0117034912109</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>90.90326690673828</v>
+        <v>90.90327453613281</v>
       </c>
       <c r="C113" t="n">
         <v>130.7608642578125</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>93.05158233642578</v>
+        <v>93.05155944824219</v>
       </c>
       <c r="C114" t="n">
         <v>133.0100402832031</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>90.25558471679688</v>
+        <v>90.25555419921875</v>
       </c>
       <c r="C115" t="n">
         <v>129.0133819580078</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>88.52416229248047</v>
+        <v>88.524169921875</v>
       </c>
       <c r="C116" t="n">
         <v>126.538459777832</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>83.72136688232422</v>
+        <v>83.72135162353516</v>
       </c>
       <c r="C117" t="n">
         <v>118.8461532592773</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>83.50344848632812</v>
+        <v>83.50343322753906</v>
       </c>
       <c r="C118" t="n">
         <v>118.5367889404297</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>92.59769439697266</v>
+        <v>92.59770202636719</v>
       </c>
       <c r="C119" t="n">
         <v>131.4464874267578</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>92.83259582519531</v>
+        <v>92.83258056640625</v>
       </c>
       <c r="C120" t="n">
         <v>130.9197387695312</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>89.52436828613281</v>
+        <v>89.52436065673828</v>
       </c>
       <c r="C122" t="n">
         <v>126.2541809082031</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>93.67648315429688</v>
+        <v>93.67649078369141</v>
       </c>
       <c r="C123" t="n">
         <v>131.1622009277344</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>99.50475311279297</v>
+        <v>99.50474548339844</v>
       </c>
       <c r="C124" t="n">
         <v>139.3227386474609</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>101.1832504272461</v>
+        <v>101.1832580566406</v>
       </c>
       <c r="C126" t="n">
         <v>140.7357788085938</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>105.2709808349609</v>
+        <v>105.2709884643555</v>
       </c>
       <c r="C127" t="n">
         <v>146.4214019775391</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>108.4190368652344</v>
+        <v>108.4190444946289</v>
       </c>
       <c r="C129" t="n">
         <v>149.8662261962891</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>99.98700714111328</v>
+        <v>99.98697662353516</v>
       </c>
       <c r="C131" t="n">
         <v>138.2107086181641</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>104.5484390258789</v>
+        <v>104.548469543457</v>
       </c>
       <c r="C132" t="n">
         <v>143.5953216552734</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>108.7062683105469</v>
+        <v>108.7062835693359</v>
       </c>
       <c r="C133" t="n">
         <v>149.3060150146484</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>106.423454284668</v>
+        <v>106.4234390258789</v>
       </c>
       <c r="C134" t="n">
         <v>146.1705627441406</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>114.1812133789062</v>
+        <v>114.1812438964844</v>
       </c>
       <c r="C135" t="n">
         <v>155.81103515625</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>117.2325744628906</v>
+        <v>117.2325973510742</v>
       </c>
       <c r="C136" t="n">
         <v>159.9749145507812</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>119.9898529052734</v>
+        <v>119.9898834228516</v>
       </c>
       <c r="C137" t="n">
         <v>163.7374572753906</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>126.0320510864258</v>
+        <v>126.0320434570312</v>
       </c>
       <c r="C138" t="n">
         <v>170.9615325927734</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>128.3250122070312</v>
+        <v>128.3249664306641</v>
       </c>
       <c r="C139" t="n">
         <v>174.0718994140625</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>123.9980163574219</v>
+        <v>123.9979858398438</v>
       </c>
       <c r="C140" t="n">
         <v>168.2023468017578</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>126.6639938354492</v>
+        <v>126.6639785766602</v>
       </c>
       <c r="C141" t="n">
         <v>170.8361206054688</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>130.1231994628906</v>
+        <v>130.1231689453125</v>
       </c>
       <c r="C142" t="n">
         <v>175.5016784667969</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>142.7015686035156</v>
+        <v>142.7015380859375</v>
       </c>
       <c r="C143" t="n">
         <v>192.466552734375</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>156.0757293701172</v>
+        <v>156.0757141113281</v>
       </c>
       <c r="C146" t="n">
         <v>209.4481658935547</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>137.5799407958984</v>
+        <v>137.5799102783203</v>
       </c>
       <c r="C148" t="n">
         <v>183.5451507568359</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>121.8302154541016</v>
+        <v>121.8301620483398</v>
       </c>
       <c r="C149" t="n">
         <v>162.533447265625</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>124.1337280273438</v>
+        <v>124.133674621582</v>
       </c>
       <c r="C151" t="n">
         <v>164.4815979003906</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>133.9775390625</v>
+        <v>133.9775543212891</v>
       </c>
       <c r="C152" t="n">
         <v>177.5250854492188</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>133.9862365722656</v>
+        <v>133.9862518310547</v>
       </c>
       <c r="C153" t="n">
         <v>176.3545074462891</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>133.8528289794922</v>
+        <v>133.8527984619141</v>
       </c>
       <c r="C154" t="n">
         <v>176.1789245605469</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>120.8620681762695</v>
+        <v>120.8620223999023</v>
       </c>
       <c r="C155" t="n">
         <v>159.0802612304688</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>132.9824829101562</v>
+        <v>132.9825134277344</v>
       </c>
       <c r="C156" t="n">
         <v>173.8461608886719</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>128.10888671875</v>
+        <v>128.1087951660156</v>
       </c>
       <c r="C158" t="n">
         <v>167.4749145507812</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>133.560546875</v>
+        <v>133.5605926513672</v>
       </c>
       <c r="C159" t="n">
         <v>173.4030151367188</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>133.8117370605469</v>
+        <v>133.8117523193359</v>
       </c>
       <c r="C160" t="n">
         <v>173.7290954589844</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>122.0457229614258</v>
+        <v>122.0457611083984</v>
       </c>
       <c r="C161" t="n">
         <v>158.4531707763672</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>103.7603530883789</v>
+        <v>103.7603302001953</v>
       </c>
       <c r="C162" t="n">
         <v>133.5702362060547</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>112.5872573852539</v>
+        <v>112.587272644043</v>
       </c>
       <c r="C163" t="n">
         <v>144.93310546875</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>113.4836273193359</v>
+        <v>113.4836196899414</v>
       </c>
       <c r="C164" t="n">
         <v>146.0869598388672</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>106.0010604858398</v>
+        <v>106.0010452270508</v>
       </c>
       <c r="C165" t="n">
         <v>135.2173919677734</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>107.7576751708984</v>
+        <v>107.757682800293</v>
       </c>
       <c r="C166" t="n">
         <v>137.4581909179688</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>112.2408905029297</v>
+        <v>112.2409133911133</v>
       </c>
       <c r="C168" t="n">
         <v>141.9481658935547</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>116.6374282836914</v>
+        <v>116.6374435424805</v>
       </c>
       <c r="C169" t="n">
         <v>147.5083618164062</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>104.8956680297852</v>
+        <v>104.8956756591797</v>
       </c>
       <c r="C170" t="n">
         <v>132.6588592529297</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>91.06881713867188</v>
+        <v>91.06885528564453</v>
       </c>
       <c r="C172" t="n">
         <v>114.1387939453125</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>101.3491744995117</v>
+        <v>101.3491668701172</v>
       </c>
       <c r="C173" t="n">
         <v>127.0234146118164</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>105.0965118408203</v>
+        <v>105.0965042114258</v>
       </c>
       <c r="C175" t="n">
         <v>130.4264221191406</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>101.3774642944336</v>
+        <v>101.3774795532227</v>
       </c>
       <c r="C176" t="n">
         <v>125.81103515625</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>110.8326034545898</v>
+        <v>110.832633972168</v>
       </c>
       <c r="C177" t="n">
         <v>136.3043518066406</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>108.9017639160156</v>
+        <v>108.9017944335938</v>
       </c>
       <c r="C178" t="n">
         <v>133.9297637939453</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>108.7522201538086</v>
+        <v>108.7522048950195</v>
       </c>
       <c r="C179" t="n">
         <v>133.7458190917969</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>118.4500427246094</v>
+        <v>118.4500732421875</v>
       </c>
       <c r="C180" t="n">
         <v>144.4230804443359</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>119.8626937866211</v>
+        <v>119.8626861572266</v>
       </c>
       <c r="C181" t="n">
         <v>146.1454925537109</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>120.4592742919922</v>
+        <v>120.4593048095703</v>
       </c>
       <c r="C182" t="n">
         <v>146.8729095458984</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>121.0370864868164</v>
+        <v>121.037109375</v>
       </c>
       <c r="C183" t="n">
         <v>146.3712310791016</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>136.3033142089844</v>
+        <v>136.3032836914062</v>
       </c>
       <c r="C185" t="n">
         <v>164.8327789306641</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>141.4156188964844</v>
+        <v>141.4155883789062</v>
       </c>
       <c r="C186" t="n">
         <v>169.7658843994141</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>138.3441009521484</v>
+        <v>138.3440856933594</v>
       </c>
       <c r="C187" t="n">
         <v>166.0785980224609</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>137.8635559082031</v>
+        <v>137.863525390625</v>
       </c>
       <c r="C188" t="n">
         <v>165.5016784667969</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>136.6701049804688</v>
+        <v>136.6701202392578</v>
       </c>
       <c r="C189" t="n">
         <v>162.8260803222656</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>123.111198425293</v>
+        <v>123.1112060546875</v>
       </c>
       <c r="C190" t="n">
         <v>146.6722412109375</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>125.3990707397461</v>
+        <v>125.3990859985352</v>
       </c>
       <c r="C191" t="n">
         <v>149.3979949951172</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>120.3066024780273</v>
+        <v>120.3066101074219</v>
       </c>
       <c r="C192" t="n">
         <v>142.1739196777344</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>117.4624252319336</v>
+        <v>117.4623947143555</v>
       </c>
       <c r="C194" t="n">
         <v>138.8127136230469</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>106.1894378662109</v>
+        <v>106.1894454956055</v>
       </c>
       <c r="C195" t="n">
         <v>124.2892990112305</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>106.3537445068359</v>
+        <v>106.3537368774414</v>
       </c>
       <c r="C196" t="n">
         <v>124.4816055297852</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>107.7243957519531</v>
+        <v>107.7243804931641</v>
       </c>
       <c r="C198" t="n">
         <v>124.8244171142578</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>93.37939453125</v>
+        <v>93.37940979003906</v>
       </c>
       <c r="C199" t="n">
         <v>108.2023391723633</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>103.3588180541992</v>
+        <v>103.3588333129883</v>
       </c>
       <c r="C200" t="n">
         <v>119.7658843994141</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>80.55264282226562</v>
+        <v>80.55265045166016</v>
       </c>
       <c r="C202" t="n">
         <v>92.39130401611328</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>91.69877624511719</v>
+        <v>91.69878387451172</v>
       </c>
       <c r="C203" t="n">
         <v>105.1755828857422</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>92.90525817871094</v>
+        <v>92.90528106689453</v>
       </c>
       <c r="C204" t="n">
         <v>105.3260879516602</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>88.44327545166016</v>
+        <v>88.44329071044922</v>
       </c>
       <c r="C205" t="n">
         <v>100.2675552368164</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>84.87368011474609</v>
+        <v>84.87369537353516</v>
       </c>
       <c r="C206" t="n">
         <v>96.22073364257812</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>80.51239013671875</v>
+        <v>80.51237487792969</v>
       </c>
       <c r="C207" t="n">
         <v>90.08361053466797</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>78.54702758789062</v>
+        <v>78.54703521728516</v>
       </c>
       <c r="C208" t="n">
         <v>87.88461303710938</v>
@@ -6005,7 +6005,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>79.37650299072266</v>
+        <v>79.37651062011719</v>
       </c>
       <c r="C209" t="n">
         <v>88.81270599365234</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>70.78900146484375</v>
+        <v>70.78900909423828</v>
       </c>
       <c r="C210" t="n">
         <v>78.01839447021484</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>75.93259429931641</v>
+        <v>75.93260955810547</v>
       </c>
       <c r="C211" t="n">
         <v>83.68729400634766</v>
@@ -6146,7 +6146,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>72.08634948730469</v>
+        <v>72.08635711669922</v>
       </c>
       <c r="C214" t="n">
         <v>78.27759552001953</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>70.03047943115234</v>
+        <v>70.03048706054688</v>
       </c>
       <c r="C215" t="n">
         <v>76.04515075683594</v>
@@ -6200,7 +6200,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>77.48322296142578</v>
+        <v>77.48321533203125</v>
       </c>
       <c r="C216" t="n">
         <v>82.83444976806641</v>
@@ -6254,7 +6254,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>73.79169464111328</v>
+        <v>73.79167938232422</v>
       </c>
       <c r="C218" t="n">
         <v>78.88796234130859</v>
@@ -6281,7 +6281,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>73.24429321289062</v>
+        <v>73.24427795410156</v>
       </c>
       <c r="C219" t="n">
         <v>77.02341461181641</v>
@@ -6308,7 +6308,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>84.33588409423828</v>
+        <v>84.33586883544922</v>
       </c>
       <c r="C220" t="n">
         <v>88.68729400634766</v>
@@ -6362,7 +6362,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>95.88803100585938</v>
+        <v>95.88801574707031</v>
       </c>
       <c r="C222" t="n">
         <v>100.1399993896484</v>
@@ -6389,7 +6389,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>97.85098266601562</v>
+        <v>97.85097503662109</v>
       </c>
       <c r="C223" t="n">
         <v>102.1900024414062</v>
@@ -6416,7 +6416,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>122.1341857910156</v>
+        <v>122.1341934204102</v>
       </c>
       <c r="C224" t="n">
         <v>127.5500030517578</v>
@@ -6445,7 +6445,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>129.6662902832031</v>
+        <v>129.6662750244141</v>
       </c>
       <c r="C225" t="n">
         <v>134.6900024414062</v>
@@ -6532,7 +6532,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>129.2332153320312</v>
+        <v>129.2332000732422</v>
       </c>
       <c r="C228" t="n">
         <v>133.5299987792969</v>
@@ -6561,7 +6561,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>124.9360809326172</v>
+        <v>124.9360885620117</v>
       </c>
       <c r="C229" t="n">
         <v>129.0899963378906</v>
@@ -6764,7 +6764,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>145.8415222167969</v>
+        <v>145.8415069580078</v>
       </c>
       <c r="C236" t="n">
         <v>149.2200012207031</v>
@@ -6851,7 +6851,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>163.4821929931641</v>
+        <v>163.482177734375</v>
       </c>
       <c r="C239" t="n">
         <v>166.5</v>
@@ -6938,7 +6938,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>151.0301666259766</v>
+        <v>151.0301818847656</v>
       </c>
       <c r="C242" t="n">
         <v>153.1600036621094</v>
